--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/region-de-los-rios.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/region-de-los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1432083-1878-CM26</t>
+          <t>1305560-12-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2547.98</v>
+        <v>31927.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3335-944-CM26</t>
+          <t>5955-44-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2209.12</v>
+        <v>9746.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3850-404-CM26</t>
+          <t>5418-21-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,43 +691,43 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2450.13</v>
+        <v>10512.29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1432083-2140-CM26</t>
+          <t>3850-85-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,6 +752,1409 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
+        <v>3923.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3850-119-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69.201.000-0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>9705.52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2910-79-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>69.200.700-k</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>7453.57</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1305560-96-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>4728.47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>926853-29-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>65.120.506-9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>2779.07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1267885-2733-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>71.016.300-6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>24169.61</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1267885-2734-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>71.016.300-6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>2852.83</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3335-515-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>10798.36</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2909-328-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.200.700-k</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>11297.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1191382-15-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.200.100-1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>16838.51</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3335-785-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>13692.14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1432083-900-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>8232.360000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1432083-905-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>10639.24</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1079694-253-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>9059.85</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1432083-1124-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>4351.07</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1432083-1162-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>8037.26</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1432083-1224-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>4053.97</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1432083-1277-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>6198.71</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1432083-1327-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>3071.34</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1432083-1395-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>31439.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1432083-1878-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>2547.98</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3335-944-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>2209.12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3850-404-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.201.000-0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>2450.13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1432083-2140-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
         <v>9492.059999999999</v>
       </c>
     </row>
